--- a/examples/slnsw_09ad5040-43cb-4a0e-88df-e63c9d04d045/data/slnsw_09ad5040-43cb-4a0e-88df-e63c9d04d045.xlsx
+++ b/examples/slnsw_09ad5040-43cb-4a0e-88df-e63c9d04d045/data/slnsw_09ad5040-43cb-4a0e-88df-e63c9d04d045.xlsx
@@ -5,30 +5,29 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="20"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="12"/>
   </bookViews>
   <sheets>
-    <sheet name="Descriptive_additional_schemas" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="Descriptive_IE" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="Descriptive_Reps" sheetId="3" state="visible" r:id="rId4"/>
-    <sheet name="Descriptive_Files" sheetId="4" state="visible" r:id="rId5"/>
-    <sheet name="Administrative_IE" sheetId="5" state="visible" r:id="rId6"/>
-    <sheet name="Administrative_Reps" sheetId="6" state="visible" r:id="rId7"/>
-    <sheet name="PREMIS_Agents" sheetId="7" state="visible" r:id="rId8"/>
-    <sheet name="PREMIS_IE_external_identifiers" sheetId="8" state="visible" r:id="rId9"/>
-    <sheet name="PREMIS_IE_events" sheetId="9" state="visible" r:id="rId10"/>
-    <sheet name="PREMIS_IE_significant_props" sheetId="10" state="visible" r:id="rId11"/>
-    <sheet name="PREMIS_IE_rights" sheetId="11" state="visible" r:id="rId12"/>
-    <sheet name="PREMIS_Rep_events" sheetId="12" state="visible" r:id="rId13"/>
-    <sheet name="PREMIS_Rep_significant_props" sheetId="13" state="visible" r:id="rId14"/>
-    <sheet name="PREMIS_Rep_rights" sheetId="14" state="visible" r:id="rId15"/>
-    <sheet name="PREMIS_Files_events" sheetId="15" state="visible" r:id="rId16"/>
-    <sheet name="PREMIS_Files_significant_props" sheetId="16" state="visible" r:id="rId17"/>
-    <sheet name="PREMIS_Files_creating_app" sheetId="17" state="visible" r:id="rId18"/>
-    <sheet name="PREMIS_Files_inhibitors" sheetId="18" state="visible" r:id="rId19"/>
-    <sheet name="PREMIS_Files_original_name" sheetId="19" state="visible" r:id="rId20"/>
-    <sheet name="PREMIS_Files_rights" sheetId="20" state="visible" r:id="rId21"/>
-    <sheet name="File_Sequence" sheetId="21" state="visible" r:id="rId22"/>
+    <sheet name="Descriptive_additional_schemas" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Descriptive_IE" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Descriptive_Reps" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Descriptive_Files" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Administrative_IE" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Administrative_Reps" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="PREMIS_Agents" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="PREMIS_IE_external_identifiers" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="PREMIS_IE_events" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="PREMIS_IE_significant_props" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="PREMIS_IE_rights" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="PREMIS_Rep_events" sheetId="12" state="visible" r:id="rId14"/>
+    <sheet name="PREMIS_Rep_significant_props" sheetId="13" state="visible" r:id="rId15"/>
+    <sheet name="PREMIS_Rep_rights" sheetId="14" state="visible" r:id="rId16"/>
+    <sheet name="PREMIS_Files_events" sheetId="15" state="visible" r:id="rId17"/>
+    <sheet name="PREMIS_Files_significant_props" sheetId="16" state="visible" r:id="rId18"/>
+    <sheet name="PREMIS_Files_creating_app" sheetId="17" state="visible" r:id="rId19"/>
+    <sheet name="PREMIS_Files_inhibitors" sheetId="18" state="visible" r:id="rId20"/>
+    <sheet name="PREMIS_Files_rights" sheetId="19" state="visible" r:id="rId21"/>
+    <sheet name="File_Sequence" sheetId="20" state="visible" r:id="rId22"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="185">
   <si>
     <t xml:space="preserve">namespace_prefix</t>
   </si>
@@ -318,7 +317,10 @@
     <t xml:space="preserve">event_date_time</t>
   </si>
   <si>
-    <t xml:space="preserve">event_detail</t>
+    <t xml:space="preserve">event_detail1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">event_detail2</t>
   </si>
   <si>
     <t xml:space="preserve">event_outcome</t>
@@ -336,6 +338,9 @@
     <t xml:space="preserve">2023-10-01T15:20:30Z</t>
   </si>
   <si>
+    <t xml:space="preserve">pre-ingest event</t>
+  </si>
+  <si>
     <t xml:space="preserve">The sketches were digitised using a digital camera.</t>
   </si>
   <si>
@@ -477,6 +482,9 @@
     <t xml:space="preserve">dissemination</t>
   </si>
   <si>
+    <t xml:space="preserve">event_detail3</t>
+  </si>
+  <si>
     <t xml:space="preserve">second_file_path</t>
   </si>
   <si>
@@ -507,43 +515,10 @@
     <t xml:space="preserve">2023-10-02T09:55:12+10:00</t>
   </si>
   <si>
-    <t xml:space="preserve">image width</t>
-  </si>
-  <si>
-    <t xml:space="preserve">image height</t>
-  </si>
-  <si>
-    <t xml:space="preserve">creating_application_name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">creating_application_version</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pluma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.26.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inhibitor_type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inhibitor_target</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inhibitor_key</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Password protection</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All content</t>
-  </si>
-  <si>
-    <t xml:space="preserve">See enterprise password manager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">original_name</t>
+    <t xml:space="preserve">filename change</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unsupported characters removed from filename and filename shortened</t>
   </si>
   <si>
     <r>
@@ -551,19 +526,53 @@
         <sz val="10"/>
         <rFont val="Arial"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">My Notes CRAZY long _filename , with dodgy characters </t>
+      <t xml:space="preserve">originalFilename:My Notes CRAZY long _filename , with dodgy characters </t>
     </r>
     <r>
       <rPr>
         <sz val="10"/>
         <rFont val="Samyak Tamil"/>
         <family val="0"/>
-        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">©.txt.txt </t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">image width</t>
+  </si>
+  <si>
+    <t xml:space="preserve">image height</t>
+  </si>
+  <si>
+    <t xml:space="preserve">creating_application_name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">creating_application_version</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pluma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.26.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inhibitor_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inhibitor_target</t>
+  </si>
+  <si>
+    <t xml:space="preserve">inhibitor_key</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Password protection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All content</t>
+  </si>
+  <si>
+    <t xml:space="preserve">See enterprise password manager</t>
   </si>
   <si>
     <t xml:space="preserve">license_terms</t>
@@ -611,7 +620,7 @@
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="166" formatCode="&quot;TRUE&quot;;&quot;TRUE&quot;;&quot;FALSE&quot;"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -656,9 +665,13 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Samyak Tamil"/>
       <family val="0"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -703,36 +716,44 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -748,38 +769,144 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="ffffff"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="ffffff"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18a303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369a3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="a33e03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8e03a3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="c99c00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="c9211e"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000ee"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551a8b"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultColWidth="11.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22.36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="43.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="46.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="43.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="46.27"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>5</v>
       </c>
     </row>
@@ -799,31 +926,31 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="27.65"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="40.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="27.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="40.01"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>105</v>
+      <c r="A1" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>106</v>
-      </c>
-      <c r="B2" s="0" t="s">
-        <v>107</v>
+      <c r="A2" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -838,179 +965,179 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AMJ5"/>
   <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="22.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="27.65"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="24.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="21.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="21.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="39.62"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="18.06"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="19.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="15.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="113.23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="16.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="23.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="22.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="27.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="24.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="21.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="21.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="39.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="18.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="19.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="15.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="113.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="16.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="23.88"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C1" s="1" t="s">
+    <row r="1" s="2" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="AMJ1" s="0"/>
+      <c r="O1" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="AMJ1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>124</v>
-      </c>
-      <c r="B2" s="0" t="s">
-        <v>125</v>
-      </c>
-      <c r="C2" s="7" t="n">
+      <c r="A2" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C2" s="8" t="n">
         <v>44927</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="G2" s="8" t="n">
+        <v>44927</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="E2" s="0" t="s">
-        <v>127</v>
-      </c>
-      <c r="F2" s="0" t="s">
+      <c r="B3" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C3" s="8" t="n">
+        <v>44927</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="G2" s="7" t="n">
+      <c r="E3" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="G3" s="8" t="n">
         <v>44927</v>
       </c>
-      <c r="H2" s="0" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>124</v>
-      </c>
-      <c r="B3" s="0" t="s">
-        <v>129</v>
-      </c>
-      <c r="C3" s="7" t="n">
-        <v>44927</v>
-      </c>
-      <c r="D3" s="0" t="s">
-        <v>126</v>
-      </c>
-      <c r="E3" s="0" t="s">
-        <v>127</v>
-      </c>
-      <c r="F3" s="0" t="s">
+      <c r="H3" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="G3" s="7" t="n">
-        <v>44927</v>
-      </c>
-      <c r="H3" s="0" t="s">
-        <v>126</v>
-      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C4" s="8" t="n">
+        <v>43831</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="I4" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B4" s="0" t="s">
-        <v>131</v>
-      </c>
-      <c r="C4" s="7" t="n">
-        <v>43831</v>
-      </c>
-      <c r="D4" s="0" t="s">
-        <v>126</v>
-      </c>
-      <c r="I4" s="0" t="s">
+      <c r="J4" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="K4" s="8" t="n">
+        <v>45108</v>
+      </c>
+      <c r="L4" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="J4" s="0" t="s">
-        <v>132</v>
-      </c>
-      <c r="K4" s="7" t="n">
-        <v>45108</v>
-      </c>
-      <c r="L4" s="0" t="s">
-        <v>126</v>
-      </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>133</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>134</v>
-      </c>
-      <c r="C5" s="5" t="n">
+      <c r="A5" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C5" s="6" t="n">
         <v>45292</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="6" t="n">
         <v>45658</v>
       </c>
-      <c r="M5" s="0" t="s">
-        <v>135</v>
-      </c>
-      <c r="N5" s="0" t="s">
-        <v>136</v>
-      </c>
-      <c r="O5" s="5" t="n">
+      <c r="M5" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="O5" s="6" t="n">
         <v>45292</v>
       </c>
-      <c r="P5" s="5" t="n">
+      <c r="P5" s="6" t="n">
         <v>45658</v>
       </c>
     </row>
@@ -1026,70 +1153,76 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="31.68"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="30.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="24.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="20.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="31.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="30.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="19.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="30.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="24.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="20.42"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>137</v>
+      <c r="I1" s="2" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>138</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>139</v>
+      <c r="A2" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>141</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>140</v>
-      </c>
-      <c r="D2" s="0" t="s">
         <v>99</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="D2" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="F2" s="0" t="s">
-        <v>100</v>
-      </c>
-      <c r="G2" s="0" t="s">
+      <c r="G2" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H2" s="0" t="s">
+      <c r="I2" s="1" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1105,71 +1238,71 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30.02"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="29.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30.02"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="29.31"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>105</v>
+      <c r="B1" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="0" t="s">
-        <v>141</v>
-      </c>
-      <c r="C2" s="0" t="n">
+      <c r="B2" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C2" s="1" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="0" t="s">
-        <v>142</v>
-      </c>
-      <c r="C3" s="0" t="s">
+      <c r="B3" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="C4" s="1" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="0" t="s">
-        <v>141</v>
-      </c>
-      <c r="C4" s="0" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>142</v>
-      </c>
-      <c r="C5" s="0" t="s">
-        <v>143</v>
+      <c r="B5" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>145</v>
       </c>
     </row>
   </sheetData>
@@ -1184,76 +1317,76 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I2"/>
   <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="24.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="41.94"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="22.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="19.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="24.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="41.94"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="22.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="19.45"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="D1" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>119</v>
       </c>
+      <c r="H1" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D2" s="8" t="n">
+        <v>43831</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C2" s="0" t="s">
-        <v>144</v>
-      </c>
-      <c r="D2" s="7" t="n">
-        <v>43831</v>
-      </c>
-      <c r="E2" s="0" t="s">
-        <v>126</v>
-      </c>
-      <c r="F2" s="0" t="s">
+      <c r="G2" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H2" s="8" t="n">
+        <v>45108</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>128</v>
-      </c>
-      <c r="G2" s="0" t="s">
-        <v>132</v>
-      </c>
-      <c r="H2" s="7" t="n">
-        <v>45108</v>
-      </c>
-      <c r="I2" s="0" t="s">
-        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -1268,262 +1401,327 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="36.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="37.23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="21.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="33.21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="24.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="54.32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="43.9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="27.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="36.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="37.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="66.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="75.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="21.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="33.21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="24.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="54.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="43.9"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>145</v>
+      <c r="J1" s="2" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>146</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>147</v>
+      <c r="A2" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>150</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>148</v>
-      </c>
-      <c r="D2" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="B3" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="F2" s="0" t="s">
-        <v>100</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>146</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="C3" s="0" t="s">
-        <v>148</v>
-      </c>
-      <c r="D3" s="0" t="s">
+      <c r="H3" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="B4" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="C4" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="G4" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="F3" s="0" t="s">
-        <v>100</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>146</v>
-      </c>
-      <c r="B4" s="7" t="s">
+      <c r="H4" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="C5" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="C4" s="0" t="s">
-        <v>148</v>
-      </c>
-      <c r="D4" s="0" t="s">
+      <c r="F5" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="B6" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="C6" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="F4" s="0" t="s">
-        <v>100</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>146</v>
-      </c>
-      <c r="B5" s="7" t="s">
+      <c r="H6" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="C7" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="C5" s="0" t="s">
-        <v>148</v>
-      </c>
-      <c r="D5" s="0" t="s">
-        <v>149</v>
-      </c>
-      <c r="E5" s="3" t="s">
+      <c r="G7" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="F5" s="0" t="s">
-        <v>100</v>
-      </c>
-      <c r="G5" s="3" t="s">
+      <c r="H7" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C8" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="I8" s="4" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>146</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="C6" s="0" t="s">
-        <v>148</v>
-      </c>
-      <c r="D6" s="0" t="s">
-        <v>149</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="F6" s="0" t="s">
-        <v>100</v>
-      </c>
-      <c r="G6" s="3" t="s">
+      <c r="J8" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C9" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="I9" s="4" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>146</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="C7" s="0" t="s">
-        <v>148</v>
-      </c>
-      <c r="D7" s="0" t="s">
-        <v>149</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="F7" s="0" t="s">
-        <v>100</v>
-      </c>
-      <c r="G7" s="3" t="s">
+      <c r="J9" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C10" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="I10" s="4" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>138</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="C8" s="0" t="s">
-        <v>140</v>
-      </c>
-      <c r="D8" s="0" t="s">
+      <c r="J10" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
+        <v>158</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>141</v>
+      </c>
+      <c r="C11" s="0" t="s">
         <v>99</v>
       </c>
-      <c r="E8" s="0" t="s">
-        <v>76</v>
-      </c>
-      <c r="F8" s="0" t="s">
-        <v>100</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>138</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="C9" s="0" t="s">
-        <v>140</v>
-      </c>
-      <c r="D9" s="0" t="s">
-        <v>99</v>
-      </c>
-      <c r="E9" s="0" t="s">
-        <v>76</v>
-      </c>
-      <c r="F9" s="0" t="s">
-        <v>100</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
-        <v>138</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="C10" s="0" t="s">
-        <v>140</v>
-      </c>
-      <c r="D10" s="0" t="s">
-        <v>99</v>
-      </c>
-      <c r="E10" s="0" t="s">
-        <v>76</v>
-      </c>
-      <c r="F10" s="0" t="s">
-        <v>100</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>50</v>
+      <c r="D11" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>160</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1538,158 +1736,158 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C13"/>
   <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="55.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="55.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="25.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="30.56"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>105</v>
+      <c r="B1" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="0" t="s">
-        <v>155</v>
-      </c>
-      <c r="C2" s="0" t="n">
+      <c r="B2" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C2" s="1" t="n">
         <v>800</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="0" t="s">
-        <v>156</v>
-      </c>
-      <c r="C3" s="0" t="n">
+      <c r="B3" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C3" s="1" t="n">
         <v>600</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B4" s="0" t="s">
-        <v>155</v>
-      </c>
-      <c r="C4" s="0" t="n">
+      <c r="B4" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C4" s="1" t="n">
         <v>800</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="0" t="s">
-        <v>156</v>
-      </c>
-      <c r="C5" s="0" t="n">
+      <c r="B5" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C5" s="1" t="n">
         <v>600</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="0" t="s">
-        <v>155</v>
-      </c>
-      <c r="C6" s="0" t="n">
+      <c r="B6" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C6" s="1" t="n">
         <v>800</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B7" s="0" t="s">
-        <v>156</v>
-      </c>
-      <c r="C7" s="0" t="n">
+      <c r="B7" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C7" s="1" t="n">
         <v>600</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B8" s="0" t="s">
-        <v>155</v>
-      </c>
-      <c r="C8" s="0" t="n">
+      <c r="B8" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C8" s="1" t="n">
         <v>800</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="0" t="s">
-        <v>156</v>
-      </c>
-      <c r="C9" s="0" t="n">
+      <c r="B9" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C9" s="1" t="n">
         <v>600</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="0" t="s">
-        <v>155</v>
-      </c>
-      <c r="C10" s="0" t="n">
+      <c r="B10" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C10" s="1" t="n">
         <v>800</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B11" s="0" t="s">
-        <v>156</v>
-      </c>
-      <c r="C11" s="0" t="n">
+      <c r="B11" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C11" s="1" t="n">
         <v>600</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B12" s="0" t="s">
-        <v>155</v>
-      </c>
-      <c r="C12" s="0" t="n">
+      <c r="B12" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="C12" s="1" t="n">
         <v>800</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B13" s="0" t="s">
-        <v>156</v>
-      </c>
-      <c r="C13" s="0" t="n">
+      <c r="B13" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="C13" s="1" t="n">
         <v>600</v>
       </c>
     </row>
@@ -1705,70 +1903,70 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="49.46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="31.81"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="35.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="49.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="31.81"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="35.43"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>158</v>
+      <c r="B1" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B3" s="0" t="s">
-        <v>159</v>
-      </c>
-      <c r="C3" s="0" t="s">
-        <v>160</v>
+      <c r="B3" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>79</v>
       </c>
     </row>
@@ -1784,45 +1982,45 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="53.35"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="32.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="24.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="41.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="53.35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="24.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="41.82"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>163</v>
+      <c r="B1" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="0" t="s">
-        <v>164</v>
-      </c>
-      <c r="C2" s="0" t="s">
-        <v>165</v>
-      </c>
-      <c r="D2" s="0" t="s">
-        <v>166</v>
+      <c r="B2" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -1837,32 +2035,151 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="57.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="61.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1024" min="1024" style="0" width="11.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="50.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="19.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="9.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="67.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="17.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="16.71"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>51</v>
-      </c>
-      <c r="B2" s="0" t="s">
-        <v>168</v>
+      <c r="B1" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D2" s="8" t="n">
+        <v>44927</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="G2" s="8" t="n">
+        <v>44927</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D3" s="8" t="n">
+        <v>44927</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="G3" s="8" t="n">
+        <v>44927</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D4" s="8" t="n">
+        <v>44927</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="G4" s="8" t="n">
+        <v>44927</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="D5" s="8" t="n">
+        <v>44927</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="G5" s="8" t="n">
+        <v>44927</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -1877,120 +2194,120 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C12"/>
   <sheetFormatPr defaultColWidth="8.76953125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="20.7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="55.7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="55.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="18.61"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>29</v>
       </c>
     </row>
@@ -2009,277 +2326,118 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="50.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="19.64"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="9.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="67.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="17.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="16.71"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" s="0" t="s">
-        <v>172</v>
-      </c>
-      <c r="C2" s="0" t="s">
-        <v>173</v>
-      </c>
-      <c r="D2" s="7" t="n">
-        <v>44927</v>
-      </c>
-      <c r="E2" s="0" t="s">
-        <v>126</v>
-      </c>
-      <c r="F2" s="0" t="s">
-        <v>174</v>
-      </c>
-      <c r="G2" s="7" t="n">
-        <v>44927</v>
-      </c>
-      <c r="H2" s="0" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="0" t="s">
-        <v>172</v>
-      </c>
-      <c r="C3" s="0" t="s">
-        <v>173</v>
-      </c>
-      <c r="D3" s="7" t="n">
-        <v>44927</v>
-      </c>
-      <c r="E3" s="0" t="s">
-        <v>126</v>
-      </c>
-      <c r="F3" s="0" t="s">
-        <v>174</v>
-      </c>
-      <c r="G3" s="7" t="n">
-        <v>44927</v>
-      </c>
-      <c r="H3" s="0" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>45</v>
-      </c>
-      <c r="B4" s="0" t="s">
-        <v>172</v>
-      </c>
-      <c r="C4" s="0" t="s">
-        <v>173</v>
-      </c>
-      <c r="D4" s="7" t="n">
-        <v>44927</v>
-      </c>
-      <c r="E4" s="0" t="s">
-        <v>126</v>
-      </c>
-      <c r="F4" s="0" t="s">
-        <v>174</v>
-      </c>
-      <c r="G4" s="7" t="n">
-        <v>44927</v>
-      </c>
-      <c r="H4" s="0" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>172</v>
-      </c>
-      <c r="C5" s="0" t="s">
-        <v>173</v>
-      </c>
-      <c r="D5" s="7" t="n">
-        <v>44927</v>
-      </c>
-      <c r="E5" s="0" t="s">
-        <v>126</v>
-      </c>
-      <c r="F5" s="0" t="s">
-        <v>174</v>
-      </c>
-      <c r="G5" s="7" t="n">
-        <v>44927</v>
-      </c>
-      <c r="H5" s="0" t="s">
-        <v>126</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C11"/>
   <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34.08"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="6.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="34.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="6.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="6.01"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>176</v>
+      <c r="B1" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C2" s="0" t="s">
-        <v>177</v>
+      <c r="C2" s="1" t="s">
+        <v>181</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="C3" s="0" t="s">
-        <v>178</v>
+      <c r="C3" s="1" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="C4" s="0" t="s">
-        <v>179</v>
+      <c r="C4" s="1" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="C5" s="0" t="s">
-        <v>180</v>
+      <c r="C5" s="1" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="1" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="0" t="n">
+      <c r="B9" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="0" t="n">
+      <c r="B10" s="1" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B11" s="0" t="n">
+      <c r="B11" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -2295,71 +2453,71 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D4"/>
   <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="23.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.81"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="23.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16.81"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18.89"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2375,238 +2533,238 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D20"/>
   <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="55.97"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="35.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="55.97"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="35.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="22.51"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="1" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="0" t="s">
+      <c r="C13" s="1" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="C14" s="1" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="0" t="s">
+      <c r="C15" s="1" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B16" s="0" t="s">
+      <c r="B16" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="0" t="s">
+      <c r="C16" s="1" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B17" s="0" t="s">
+      <c r="B17" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C17" s="0" t="s">
+      <c r="C17" s="1" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B18" s="0" t="s">
+      <c r="B18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C18" s="0" t="s">
+      <c r="C18" s="1" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B19" s="0" t="s">
+      <c r="B19" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C19" s="0" t="s">
+      <c r="C19" s="1" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
+      <c r="A20" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B20" s="0" t="s">
+      <c r="B20" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="0" t="s">
+      <c r="C20" s="1" t="s">
         <v>52</v>
       </c>
     </row>
@@ -2622,70 +2780,70 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="29.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="65.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="29.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="65.86"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" s="3" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+    <row r="2" s="4" customFormat="true" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B6" s="5" t="n">
+      <c r="B6" s="6" t="n">
         <v>45413</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>63</v>
       </c>
     </row>
@@ -2701,69 +2859,69 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="32.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32.09"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="7" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="7" t="s">
         <v>69</v>
       </c>
     </row>
@@ -2779,99 +2937,99 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="27.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="23.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="24.04"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="19.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="27.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="23.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="24.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="14.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="19.04"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E4" s="0" t="n">
+      <c r="E4" s="1" t="n">
         <v>1.1</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" s="1" t="s">
         <v>88</v>
       </c>
     </row>
@@ -2887,23 +3045,23 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="41.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="41.82"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="12.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>12</v>
       </c>
     </row>
@@ -2922,79 +3080,89 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultColWidth="11.6875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="79.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.58"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="34.06"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="26.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="26.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="31.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="79.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="19.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="34.06"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="26.66"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="G1" s="1"/>
+      <c r="G1" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>96</v>
-      </c>
-      <c r="B2" s="7" t="s">
+      <c r="A2" s="1" t="s">
         <v>97</v>
       </c>
+      <c r="B2" s="8" t="s">
+        <v>98</v>
+      </c>
       <c r="C2" s="0" t="s">
-        <v>98</v>
-      </c>
-      <c r="D2" s="0" t="s">
         <v>99</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="D2" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="F2" s="0" t="s">
-        <v>100</v>
+      <c r="G2" s="1" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="C3" s="0" t="s">
+        <v>99</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="F3" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>102</v>
-      </c>
-      <c r="C3" s="0" t="s">
-        <v>103</v>
-      </c>
-      <c r="D3" s="0" t="s">
-        <v>99</v>
-      </c>
-      <c r="E3" s="0" t="s">
-        <v>80</v>
-      </c>
-      <c r="F3" s="0" t="s">
-        <v>100</v>
       </c>
     </row>
   </sheetData>
